--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -637,7 +637,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:20</t>
+          <t>Start: 13:00 • Slutt: 14:50</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:00</t>
+          <t>Start: 14:30 • Slutt: 16:20</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:35</t>
+          <t>Start: 13:00 • Slutt: 14:50</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:00 • Slutt: 18:35</t>
+          <t>Start: 16:00 • Slutt: 17:50</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:00 • Slutt: 19:20</t>
+          <t>Start: 17:00 • Slutt: 18:50</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 14:20</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 11:50 • Slutt: 13:30</t>
+          <t>Start: 13:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:00 • Slutt: 19:35</t>
+          <t>Start: 17:00 • Slutt: 18:50</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:50</t>
+          <t>Start: 14:30 • Slutt: 16:20</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:00</t>
+          <t>Start: 13:30 • Slutt: 15:20</t>
         </is>
       </c>
     </row>
@@ -12697,7 +12697,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:30</t>
+          <t>Start: 15:30 • Slutt: 17:20</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16922,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:50</t>
+          <t>Start: 14:30 • Slutt: 16:20</t>
         </is>
       </c>
     </row>
@@ -20440,7 +20440,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:10</t>
+          <t>Start: 15:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:35</t>
+          <t>Start: 13:00 • Slutt: 14:50</t>
         </is>
       </c>
     </row>
@@ -24570,7 +24570,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:50</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -25952,7 +25952,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:50</t>
+          <t>Start: 15:00 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:00</t>
+          <t>Start: 15:00 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -28032,7 +28032,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:30 • Slutt: 19:10</t>
+          <t>Start: 17:30 • Slutt: 18:50</t>
         </is>
       </c>
     </row>
@@ -29430,7 +29430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:20</t>
+          <t>Start: 13:00 • Slutt: 14:50</t>
         </is>
       </c>
     </row>
@@ -30828,7 +30828,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:50</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:00 • Slutt: 18:20</t>
+          <t>Start: 16:00 • Slutt: 17:50</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32030,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:20</t>
+          <t>Start: 13:00 • Slutt: 14:50</t>
         </is>
       </c>
     </row>
@@ -34435,7 +34435,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:30 • Slutt: 19:10</t>
+          <t>Start: 17:30 • Slutt: 18:50</t>
         </is>
       </c>
     </row>
@@ -37468,7 +37468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 18:05</t>
+          <t>Start: 15:30 • Slutt: 17:20</t>
         </is>
       </c>
     </row>
@@ -40043,7 +40043,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:50</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -41514,7 +41514,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:20</t>
+          <t>Start: 15:00 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -43522,7 +43522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:00</t>
+          <t>Start: 15:00 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -50577,7 +50577,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:10</t>
+          <t>Start: 15:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -51366,7 +51366,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 15:05</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -53179,7 +53179,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:10</t>
+          <t>Start: 15:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -54829,7 +54829,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:30</t>
+          <t>Start: 12:00 • Slutt: 13:20</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -3634,7 +3634,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 11:45 • Slutt: 13:25</t>
+          <t>Start: 11:55 • Slutt: 13:35</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 11:45 • Slutt: 13:25</t>
+          <t>Start: 11:55 • Slutt: 13:35</t>
         </is>
       </c>
     </row>
@@ -27853,7 +27853,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 11:45 • Slutt: 13:25</t>
+          <t>Start: 11:55 • Slutt: 13:35</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:20 • Slutt: 14:00</t>
+          <t>Start: 12:20 • Slutt: 15:00</t>
         </is>
       </c>
     </row>
@@ -46791,7 +46791,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:25 • Slutt: 14:45</t>
+          <t>Start: 12:45 • Slutt: 14:45</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -5626,7 +5626,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:20</t>
+          <t>Start: 15:00 • Slutt: 17:19</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:10</t>
+          <t>Start: 12:30 • Slutt: 14:09</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:15 • Slutt: 16:50</t>
+          <t>Start: 14:15 • Slutt: 16:49</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:30 • Slutt: 15:10</t>
+          <t>Start: 13:30 • Slutt: 15:09</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13038,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:15 • Slutt: 16:35</t>
+          <t>Start: 14:15 • Slutt: 16:34</t>
         </is>
       </c>
     </row>
@@ -55187,7 +55187,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:35</t>
+          <t>Start: 15:00 • Slutt: 17:34</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -13549,7 +13549,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:45 • Slutt: 19:25</t>
+          <t>Start: 17:45 • Slutt: 19:30</t>
         </is>
       </c>
     </row>
@@ -15192,7 +15192,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
+          <t>Deltakende lag: Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Ringerike 4, Ringerike 2</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -15339,12 +15339,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -15357,12 +15357,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -15375,12 +15375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -16060,7 +16060,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:00 • Slutt: 16:35</t>
+          <t>Start: 14:10 • Slutt: 16:45</t>
         </is>
       </c>
     </row>
@@ -17694,7 +17694,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:50 • Slutt: 19:25</t>
+          <t>Start: 16:55 • Slutt: 19:30</t>
         </is>
       </c>
     </row>
@@ -23939,7 +23939,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06.03.2027 (lørdag) — U12 — Baerum ishall</t>
+          <t>(AVLYST) 06.03.2027 (lørdag) — U12 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -26293,7 +26293,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:00 • Slutt: 18:20</t>
+          <t>Start: 16:10 • Slutt: 18:30</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 18:20 • Slutt: 20:00</t>
+          <t>Start: 18:30 • Slutt: 20:10</t>
         </is>
       </c>
     </row>
@@ -27154,7 +27154,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:20 • Slutt: 16:00</t>
+          <t>Start: 14:30 • Slutt: 16:10</t>
         </is>
       </c>
     </row>
@@ -29409,7 +29409,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>07.11.2026 (lørdag) — U10 — Askerhallen</t>
+          <t>(AVLYST) 07.11.2026 (lørdag) — U10 — Askerhallen</t>
         </is>
       </c>
     </row>
@@ -30291,7 +30291,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:20 • Slutt: 19:55</t>
+          <t>Start: 17:30 • Slutt: 20:00</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>08.11.2026 (søndag) — U10 — Askerhallen</t>
+          <t>(AVLYST) 08.11.2026 (søndag) — U10 — Askerhallen</t>
         </is>
       </c>
     </row>
@@ -33732,7 +33732,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>14.11.2026 (lørdag) — U11 — Baerum ishall</t>
+          <t>(AVLYST) 14.11.2026 (lørdag) — U11 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -33753,7 +33753,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:20 • Slutt: 19:40</t>
+          <t>Start: 17:30 • Slutt: 19:50</t>
         </is>
       </c>
     </row>
@@ -34772,7 +34772,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>15.11.2026 (søndag) — U12 — Jar Isforum</t>
+          <t>(AVLYST) 15.11.2026 (søndag) — U12 — Jar Isforum</t>
         </is>
       </c>
     </row>
@@ -36496,7 +36496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21.11.2026 (lørdag) — U9 — Baerum ishall</t>
+          <t>(AVLYST) 21.11.2026 (lørdag) — U9 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -40363,7 +40363,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>22.11.2026 (søndag) — U9 — Jar Isforum</t>
+          <t>(AVLYST) 22.11.2026 (søndag) — U9 — Jar Isforum</t>
         </is>
       </c>
     </row>
@@ -45245,7 +45245,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:00 • Slutt: 18:35</t>
+          <t>Start: 16:15 • Slutt: 18:50</t>
         </is>
       </c>
     </row>
@@ -46286,7 +46286,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:20 • Slutt: 16:00</t>
+          <t>Start: 14:30 • Slutt: 16:10</t>
         </is>
       </c>
     </row>
@@ -47132,7 +47132,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:00 • Slutt: 16:35</t>
+          <t>Start: 14:10 • Slutt: 16:45</t>
         </is>
       </c>
     </row>
@@ -48424,7 +48424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:00 • Slutt: 18:35</t>
+          <t>Start: 16:00 • Slutt: 18:36</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -5278,7 +5278,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Jutul Rød, Jar Rød</t>
+          <t>Deltakende lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Holmen Hockey Rød</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -19119,8 +19119,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -19141,7 +19141,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
+          <t>Deltakende lag: Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Holmen Hockey Hvit, Ringerike 1, Jar Hvit</t>
         </is>
       </c>
     </row>
@@ -19198,12 +19198,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -19216,12 +19216,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -19234,12 +19234,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -28903,7 +28903,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar Gul, Frisk Asker 1, Jar Hvit, Jutul Grønn, Jar Svart, Tønsberg Rød</t>
+          <t>Deltakende lag: Jar Gul, Frisk Asker 1, Jar Hvit, Jutul Grønn, Skien, Tønsberg Rød</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -29001,7 +29001,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -29019,7 +29019,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -29055,7 +29055,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -29086,7 +29086,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -29109,7 +29109,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -29145,7 +29145,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -29163,7 +29163,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -37120,7 +37120,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Deltakende lag: Jar Svart, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
     </row>
@@ -37159,12 +37159,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -37177,12 +37177,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringerike Svart</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -37195,12 +37195,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Ringerike Svart</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -37213,12 +37213,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -37231,12 +37231,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ringerike Svart</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -37249,12 +37249,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike Svart</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -37303,7 +37303,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -37326,7 +37326,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike Svart</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -37357,12 +37357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike Svart</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -37380,7 +37380,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ringerike Svart</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike Svart</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -37411,7 +37411,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -45669,7 +45669,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Holmen Hockey Hvit, Frisk Asker 1, Holmen Hockey Rød, Jutul Rød, Kongsberg, Ringerike 1, Frisk Asker 4, Skien</t>
+          <t>Deltakende lag: Holmen Hockey Hvit, Frisk Asker 1, Holmen Hockey Rød, Jutul Rød, Kongsberg, Ringerike 1, Frisk Asker 4, Sandefjord</t>
         </is>
       </c>
     </row>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -45821,7 +45821,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -45857,7 +45857,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -45983,7 +45983,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -46019,7 +46019,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -51359,7 +51359,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker 1, Frisk Asker 4, Jar Hvit, Jutul Grønn, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Sandefjord</t>
+          <t>Deltakende lag: Frisk Asker 1, Frisk Asker 4, Jar Hvit, Jutul Grønn, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Skien</t>
         </is>
       </c>
     </row>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -51493,7 +51493,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -51583,7 +51583,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -51619,7 +51619,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -51745,7 +51745,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D26" t="n">

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -16484,7 +16484,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
+          <t>Deltakende lag: Ringerike 1, Jutul Rød, Skien, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
         </is>
       </c>
     </row>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16613,12 +16613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -16631,12 +16631,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -16649,12 +16649,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -16667,12 +16667,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -16685,12 +16685,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -16703,12 +16703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -16721,12 +16721,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -16757,12 +16757,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -16775,12 +16775,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -16847,12 +16847,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -16865,7 +16865,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -21043,7 +21043,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
+          <t>Deltakende lag: Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Frisk Asker 3, Frisk Asker 2</t>
         </is>
       </c>
     </row>
@@ -21105,7 +21105,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -21177,7 +21177,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -21195,7 +21195,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -24111,7 +24111,7 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -24132,7 +24132,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Deltakende lag: Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Skien, Tønsberg</t>
         </is>
       </c>
     </row>
@@ -24225,7 +24225,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24302,7 +24302,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -24356,7 +24356,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -24410,7 +24410,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -32974,7 +32974,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Deltakende lag: Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Ringerike 1, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
     </row>
@@ -33067,7 +33067,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -33126,7 +33126,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -33180,7 +33180,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -33234,7 +33234,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -33360,7 +33360,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D26" t="n">

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -1832,7 +1832,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Tønsberg Hvit, Jar Lilla, Jar Gul, Holmen Hockey Hvit, Skien, Ringerike Gul</t>
+          <t>Deltakende lag: Kongsberg, Jar Lilla, Jar Gul, Holmen Hockey Hvit, Skien, Ringerike Gul</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ringerike Gul</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Kongsberg, Jar Blå, Frisk Asker 2, Jar Oransje, Holmen Hockey Hvit, Frisk Asker 1</t>
+          <t>Deltakende lag: Kongsberg, Sandefjord, Frisk Asker 2, Jar Oransje, Holmen Hockey Hvit, Frisk Asker 1</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10861,7 +10861,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
+          <t>Deltakende lag: Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Tønsberg Hvit, Ringerike Svart, Jar Lilla</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -12690,7 +12690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
+          <t>Deltakende lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -19891,7 +19891,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
@@ -19913,7 +19913,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Deltakende lag: Ringerike 2, Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg</t>
         </is>
       </c>
     </row>
@@ -19952,12 +19952,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -19988,7 +19988,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -20024,12 +20024,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -23411,8 +23411,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -23433,7 +23433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
+          <t>Deltakende lag: Ringerike 1, Ringerike 2, Jutul/Jar Kittens, Frisk Asker Svart</t>
         </is>
       </c>
     </row>
@@ -23477,7 +23477,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23567,7 +23567,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -30642,7 +30642,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Deltakende lag: Ringerike 2, Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens</t>
         </is>
       </c>
     </row>
@@ -30686,7 +30686,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -30717,7 +30717,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="D12" t="n">

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -15170,8 +15170,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -15192,7 +15192,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Ringerike 4, Ringerike 2</t>
+          <t>Deltakende lag: Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Holmen Hockey Sort, Jar Grønn</t>
         </is>
       </c>
     </row>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="D21" t="n">

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -75,10 +75,10 @@
     <sheet name="06.12 U9 Bugården ishall" sheetId="66" state="visible" r:id="rId66"/>
     <sheet name="06.12 U8 Tonsberghallen" sheetId="67" state="visible" r:id="rId67"/>
     <sheet name="12.12 U8 Baerum ishall" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="12.12 JU12 Skien ishall" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="12.12 U12 Baerum ishall" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="12.12 JU10 Schjongshallen" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="12.12 U11 Schjongshallen" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="12.12 U12 Baerum ishall" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="12.12 JU10 Schjongshallen" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="12.12 U11 Schjongshallen" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="13.12 JU12 Skien ishall" sheetId="72" state="visible" r:id="rId72"/>
     <sheet name="13.12 U9 Baerum ishall" sheetId="73" state="visible" r:id="rId73"/>
     <sheet name="13.12 U10 Schjongshallen" sheetId="74" state="visible" r:id="rId74"/>
     <sheet name="13.12 U12 Tonsberghallen" sheetId="75" state="visible" r:id="rId75"/>
@@ -45471,36 +45471,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — JU12 — Skien ishall</t>
+          <t>12.12.2026 (lørdag) — U12 — Baerum ishall</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vertsklubb: Skien</t>
+          <t>Vertsklubb: Jutul</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
+          <t>Deltakende lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:40 • Slutt: 15:20</t>
+          <t>Start: 14:30 • Slutt: 16:10</t>
         </is>
       </c>
     </row>
@@ -45532,12 +45532,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -45550,12 +45550,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -45568,12 +45568,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -45586,12 +45586,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -45604,12 +45604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -45622,12 +45622,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -46077,40 +46077,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — U12 — Baerum ishall</t>
+          <t>12.12.2026 (lørdag) — JU10 — Schjongshallen</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vertsklubb: Jutul</t>
+          <t>Vertsklubb: Ringerike</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
+          <t>Deltakende lag: Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:10</t>
+          <t>Start: 10:00 • Slutt: 12:20</t>
         </is>
       </c>
     </row>
@@ -46142,12 +46142,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Jar Rød</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -46160,12 +46160,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -46178,12 +46178,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -46219,7 +46219,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -46232,7 +46232,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -46242,6 +46242,153 @@
       </c>
       <c r="D12" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Frisk Asker Orange</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Frisk Asker Orange</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -46260,15 +46407,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — JU10 — Schjongshallen</t>
+          <t>12.12.2026 (lørdag) — U11 — Schjongshallen</t>
         </is>
       </c>
     </row>
@@ -46282,14 +46429,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
+          <t>Deltakende lag: Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 10:00 • Slutt: 12:20</t>
+          <t>Start: 12:45 • Slutt: 14:45</t>
         </is>
       </c>
     </row>
@@ -46321,12 +46468,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -46339,12 +46486,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -46353,20 +46500,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -46375,66 +46522,66 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -46443,16 +46590,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -46461,98 +46608,110 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
-        </is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
-        </is>
+          <t>Jar Gul</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
-        </is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Ringerike Gul</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
-        </is>
+          <t>Jar Gul</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -46561,13 +46720,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(Pause)</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
-        </is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -46582,40 +46744,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>12.12.2026 (lørdag) — U11 — Schjongshallen</t>
+          <t>13.12.2026 (søndag) — JU12 — Skien ishall</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vertsklubb: Ringerike</t>
+          <t>Vertsklubb: Skien</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
+          <t>Deltakende lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:45 • Slutt: 14:45</t>
+          <t>Start: 13:15 • Slutt: 15:00</t>
         </is>
       </c>
     </row>
@@ -46647,12 +46809,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -46665,12 +46827,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ringerike Gul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -46679,20 +46841,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -46701,214 +46863,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ringerike Gul</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jar Gul</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ringerike Gul</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ringerike Gul</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Jar Gul</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Ringerike Gul</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jar Gul</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -4765,7 +4765,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:50</t>
+          <t>Start: 11:30 • Slutt: 13:50</t>
         </is>
       </c>
     </row>
@@ -30023,7 +30023,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:00 • Slutt: 15:00</t>
+          <t>Start: 14:00 • Slutt: 15:50</t>
         </is>
       </c>
     </row>
@@ -33144,7 +33144,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 14:00</t>
+          <t>Start: 12:00 • Slutt: 13:50</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -25952,7 +25952,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 11:00 • Slutt: 13:35</t>
+          <t>Start: 10:30 • Slutt: 13:00</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -2091,7 +2091,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:20</t>
+          <t>Start: 13:30 • Slutt: 15:50</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 10:30 • Slutt: 12:50</t>
+          <t>Start: 10:30 • Slutt: 13:00</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 14:50</t>
+          <t>Start: 13:00 • Slutt: 15:20</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:00 • Slutt: 18:50</t>
+          <t>Start: 16:30 • Slutt: 18:50</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:19</t>
+          <t>Start: 15:00 • Slutt: 17:20</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 13:50</t>
+          <t>Start: 12:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:09</t>
+          <t>Start: 12:30 • Slutt: 14:10</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:15 • Slutt: 16:49</t>
+          <t>Start: 14:15 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:20</t>
+          <t>Start: 14:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:30 • Slutt: 15:09</t>
+          <t>Start: 13:30 • Slutt: 15:10</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:30 • Slutt: 15:20</t>
+          <t>Start: 13:00 • Slutt: 14:50</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:20</t>
+          <t>Start: 15:00 • Slutt: 17:20</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:15 • Slutt: 16:34</t>
+          <t>Start: 14:15 • Slutt: 16:35</t>
         </is>
       </c>
     </row>
@@ -13950,9 +13950,9 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -13973,7 +13973,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Deltakende lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14066,12 +14066,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -16743,7 +16743,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:30 • Slutt: 16:20</t>
+          <t>Start: 14:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:35</t>
+          <t>Start: 13:00 • Slutt: 16:00</t>
         </is>
       </c>
     </row>
@@ -21392,7 +21392,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 10:30 • Slutt: 12:50</t>
+          <t>Start: 10:30 • Slutt: 13:00</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:30 • Slutt: 19:50</t>
+          <t>Start: 17:30 • Slutt: 20:00</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 13:50</t>
+          <t>Start: 12:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -25611,7 +25611,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 16:50</t>
+          <t>Start: 15:30 • Slutt: 17:50</t>
         </is>
       </c>
     </row>
@@ -27393,9 +27393,9 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -27416,14 +27416,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Deltakende lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 13:00 • Slutt: 15:00</t>
+          <t>Start: 13:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -27460,7 +27460,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -27509,12 +27509,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -27602,7 +27602,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 16:50</t>
+          <t>Start: 14:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -30172,9 +30172,9 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -30195,7 +30195,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Deltakende lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
     </row>
@@ -30239,7 +30239,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -30252,7 +30252,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -30288,12 +30288,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -30739,7 +30739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 13:50</t>
+          <t>Start: 12:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:30 • Slutt: 18:50</t>
+          <t>Start: 16:30 • Slutt: 19:00</t>
         </is>
       </c>
     </row>
@@ -33323,7 +33323,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 14:20</t>
+          <t>Start: 12:00 • Slutt: 14:30</t>
         </is>
       </c>
     </row>
@@ -34005,7 +34005,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:20</t>
+          <t>Start: 15:00 • Slutt: 17:30</t>
         </is>
       </c>
     </row>
@@ -35062,7 +35062,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 16:40</t>
+          <t>Start: 15:00 • Slutt: 17:00</t>
         </is>
       </c>
     </row>
@@ -35241,7 +35241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:20</t>
+          <t>Start: 15:00 • Slutt: 17:30</t>
         </is>
       </c>
     </row>
@@ -35553,8 +35553,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -35575,7 +35575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
+          <t>Deltakende lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Ringerike 1, Skien</t>
         </is>
       </c>
     </row>
@@ -35614,7 +35614,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -35668,7 +35668,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -35691,7 +35691,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -35740,7 +35740,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -35776,12 +35776,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
     </row>
@@ -35829,7 +35829,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
     </row>
@@ -37379,7 +37379,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:30 • Slutt: 17:20</t>
+          <t>Start: 15:00 • Slutt: 17:20</t>
         </is>
       </c>
     </row>
@@ -39867,7 +39867,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 13:50</t>
+          <t>Start: 12:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -41338,7 +41338,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 16:50</t>
+          <t>Start: 14:30 • Slutt: 16:50</t>
         </is>
       </c>
     </row>
@@ -41858,7 +41858,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 14:20</t>
+          <t>Start: 12:00 • Slutt: 14:30</t>
         </is>
       </c>
     </row>
@@ -42169,9 +42169,9 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -42192,7 +42192,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Deltakende lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
     </row>
@@ -42236,7 +42236,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -42249,7 +42249,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -42285,12 +42285,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -42308,7 +42308,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -43346,7 +43346,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 16:50</t>
+          <t>Start: 14:00 • Slutt: 16:20</t>
         </is>
       </c>
     </row>
@@ -43687,7 +43687,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:30 • Slutt: 14:10</t>
+          <t>Start: 12:30 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -43866,7 +43866,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 14:20</t>
+          <t>Start: 12:00 • Slutt: 14:30</t>
         </is>
       </c>
     </row>
@@ -48248,7 +48248,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 16:00 • Slutt: 18:36</t>
+          <t>Start: 16:00 • Slutt: 18:35</t>
         </is>
       </c>
     </row>
@@ -51190,7 +51190,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 12:00 • Slutt: 13:50</t>
+          <t>Start: 12:00 • Slutt: 14:20</t>
         </is>
       </c>
     </row>
@@ -54371,9 +54371,9 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -54394,7 +54394,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Deltakende lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
     </row>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -54451,7 +54451,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -54487,12 +54487,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -54510,7 +54510,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -54759,7 +54759,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 15:00 • Slutt: 17:34</t>
+          <t>Start: 15:00 • Slutt: 17:35</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -23850,7 +23850,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>(AVLYST) 06.03.2027 (lørdag) — U12 — Baerum ishall</t>
+          <t>06.03.2027 (lørdag) — U12 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -23871,7 +23871,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 14:20 • Slutt: 16:00</t>
+          <t>Start: 18:15 • Slutt: 19:55</t>
         </is>
       </c>
     </row>
@@ -33643,7 +33643,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>(AVLYST) 14.11.2026 (lørdag) — U11 — Baerum ishall</t>
+          <t>14.11.2026 (lørdag) — U11 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -36407,7 +36407,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>(AVLYST) 21.11.2026 (lørdag) — U9 — Baerum ishall</t>
+          <t>21.11.2026 (lørdag) — U9 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -36428,7 +36428,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Start: 17:20 • Slutt: 19:55</t>
+          <t>Start: 17:30 • Slutt: 20:00</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond_games.xlsx
+++ b/latest/season_plan_spond_games.xlsx
@@ -23850,7 +23850,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06.03.2027 (lørdag) — U12 — Baerum ishall</t>
+          <t>(AVLYST) 06.03.2027 (lørdag) — U12 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -33643,7 +33643,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>14.11.2026 (lørdag) — U11 — Baerum ishall</t>
+          <t>(AVLYST) 14.11.2026 (lørdag) — U11 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -36407,7 +36407,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21.11.2026 (lørdag) — U9 — Baerum ishall</t>
+          <t>(AVLYST) 21.11.2026 (lørdag) — U9 — Baerum ishall</t>
         </is>
       </c>
     </row>
